--- a/artfynd/A 36912-2024 artfynd.xlsx
+++ b/artfynd/A 36912-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119585230</v>
+        <v>119585120</v>
       </c>
       <c r="B2" t="n">
-        <v>90562</v>
+        <v>57463</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,43 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Lillberget, Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>576827</v>
+        <v>576880</v>
       </c>
       <c r="R2" t="n">
-        <v>7053657</v>
+        <v>7053741</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119585120</v>
+        <v>119585230</v>
       </c>
       <c r="B3" t="n">
-        <v>57463</v>
+        <v>90562</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,43 +812,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lillberget, Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>576880</v>
+        <v>576827</v>
       </c>
       <c r="R3" t="n">
-        <v>7053741</v>
+        <v>7053657</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 36912-2024 artfynd.xlsx
+++ b/artfynd/A 36912-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119585120</v>
+        <v>119585230</v>
       </c>
       <c r="B2" t="n">
-        <v>57463</v>
+        <v>90562</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,43 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Lillberget, Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>576880</v>
+        <v>576827</v>
       </c>
       <c r="R2" t="n">
-        <v>7053741</v>
+        <v>7053657</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119585230</v>
+        <v>119585120</v>
       </c>
       <c r="B3" t="n">
-        <v>90562</v>
+        <v>57463</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,34 +803,43 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lillberget, Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>576827</v>
+        <v>576880</v>
       </c>
       <c r="R3" t="n">
-        <v>7053657</v>
+        <v>7053741</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 36912-2024 artfynd.xlsx
+++ b/artfynd/A 36912-2024 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119585120</v>
+        <v>119585230</v>
       </c>
       <c r="B2" t="n">
-        <v>57463</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,43 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Lillberget, Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>576880</v>
+        <v>576827</v>
       </c>
       <c r="R2" t="n">
-        <v>7053741</v>
+        <v>7053657</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,15 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119585230</v>
+        <v>119585120</v>
       </c>
       <c r="B3" t="n">
-        <v>90562</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,34 +793,43 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lillberget, Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>576827</v>
+        <v>576880</v>
       </c>
       <c r="R3" t="n">
-        <v>7053657</v>
+        <v>7053741</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,7 +861,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +871,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 36912-2024 artfynd.xlsx
+++ b/artfynd/A 36912-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119585230</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -895,8 +905,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119585120</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>